--- a/uploads/9093d028-2873-4fae-8561-d1a2fa309cfa/materials_summary.xlsx
+++ b/uploads/9093d028-2873-4fae-8561-d1a2fa309cfa/materials_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка по элементам" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка по элементам" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,15 +433,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,15 +465,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Класс бетона</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Морозостойкость</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Водонепроницаемость</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Количество, шт</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Объем, м³</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
@@ -492,15 +510,30 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -522,13 +555,28 @@
           <t>Бетон В30</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>В30</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>F150</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>643698.583</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>1265682.415</v>
       </c>
     </row>
@@ -548,15 +596,30 @@
           <t>Бетон</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -578,15 +641,30 @@
           <t>Бетон В30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>В30</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -608,13 +686,28 @@
           <t>Бетон</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.364</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>8.449</v>
       </c>
     </row>
@@ -634,14 +727,29 @@
           <t>Бетон В10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>66230.083</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>5278.995</v>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>В10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>66216.485</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>5002.652</v>
       </c>
     </row>
     <row r="8">
@@ -657,17 +765,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Бетон В25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>2258957.128</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>23970.997</v>
+          <t>Бетон В10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>В10</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>13.597</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>276.342</v>
       </c>
     </row>
     <row r="9">
@@ -683,17 +806,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Бетон В30</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
+          <t>Бетон В25</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>В25</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>272423.156</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>10344.024</v>
+      <c r="H9" s="2" t="n">
+        <v>2243920.319</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>23628.758</v>
       </c>
     </row>
     <row r="10">
@@ -709,17 +847,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Бетон В35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>390381.593</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>4568.696</v>
+          <t>Бетон В25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>В25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>F100</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>15036.81</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>342.239</v>
       </c>
     </row>
     <row r="11">
@@ -735,58 +888,84 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Не указан</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>8869.183000000001</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>5640.589</v>
+          <t>Бетон В30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>В30</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>F150</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>272423.156</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>10344.024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Проемы</t>
+          <t>Перекрытия</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IfcOpeningElement</t>
+          <t>IfcSlab</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Не указан</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>490</v>
+          <t>Бетон В35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>В35</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>F150</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>390381.593</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>4568.696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Прочие_элементы</t>
+          <t>Перекрытия</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcSlab</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -794,8 +973,10 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>1291</v>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -806,58 +987,105 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>8869.183000000001</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>5640.589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Стены</t>
+          <t>Проемы</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IfcWall</t>
+          <t>IfcOpeningElement</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Бетон В30</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>984</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1752340.901</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>15738.991</v>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Стены</t>
+          <t>Прочие_элементы</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>IfcWall</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Бетон В35</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>611238.9129999999</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>4514.428</v>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -873,16 +1101,113 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>Бетон В30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>В30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>F150</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>984</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1752340.901</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>15738.991</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Стены</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>В35</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>F150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>611238.9129999999</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>4514.428</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Стены</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>30568.661</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>2715.508</v>
       </c>
     </row>

--- a/uploads/9093d028-2873-4fae-8561-d1a2fa309cfa/materials_summary.xlsx
+++ b/uploads/9093d028-2873-4fae-8561-d1a2fa309cfa/materials_summary.xlsx
@@ -433,18 +433,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,30 +462,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Класс бетона</t>
+          <t>Количество, шт</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Морозостойкость</t>
+          <t>Объем, м³</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Водонепроницаемость</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Количество, шт</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Объем, м³</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
@@ -510,10 +492,8 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -521,19 +501,6 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -552,31 +519,16 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Бетон В30</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>В30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>F150</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
+          <t>Бетон В30 F150 W6</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>643698.583</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>1265682.415</v>
       </c>
     </row>
@@ -596,10 +548,8 @@
           <t>Бетон</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -607,19 +557,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -641,10 +578,8 @@
           <t>Бетон В30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>В30</t>
-        </is>
+      <c r="D5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -652,19 +587,6 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -686,28 +608,13 @@
           <t>Бетон</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+      <c r="D6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>0.364</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>8.449</v>
       </c>
     </row>
@@ -727,28 +634,13 @@
           <t>Бетон В10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>В10</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
+      <c r="D7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>66216.485</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>5002.652</v>
       </c>
     </row>
@@ -765,31 +657,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Бетон В10</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>В10</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
+          <t>Бетон В10 W6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>13.597</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>276.342</v>
       </c>
     </row>
@@ -806,32 +683,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Бетон В25</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>В25</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>F100</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2243920.319</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>23628.758</v>
+          <t>Бетон В25 F100 W4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>15036.81</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>342.239</v>
       </c>
     </row>
     <row r="10">
@@ -847,32 +709,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Бетон В25</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>В25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>F100</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>15036.81</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>342.239</v>
+          <t>Бетон В25 F100 W6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2243920.319</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>23628.758</v>
       </c>
     </row>
     <row r="11">
@@ -888,31 +735,16 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Бетон В30</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>В30</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>F150</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
+          <t>Бетон В30 F150 W6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>272423.156</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>10344.024</v>
       </c>
     </row>
@@ -929,31 +761,16 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Бетон В35</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>В35</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>F150</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
+          <t>Бетон В35 F150 W6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>390381.593</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>4568.696</v>
       </c>
     </row>
@@ -973,28 +790,13 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
+      <c r="D13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>8869.183000000001</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>5640.589</v>
       </c>
     </row>
@@ -1014,10 +816,8 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="2" t="n">
+        <v>335</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1025,19 +825,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>490</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1046,12 +833,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Прочие_элементы</t>
+          <t>Проемы</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcOpeningElement</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1059,10 +846,8 @@
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1070,19 +855,6 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1291</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1091,83 +863,61 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Стены</t>
+          <t>Проемы</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>IfcWall</t>
+          <t>IfcOpeningElement</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Бетон В30</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>В30</t>
-        </is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>152</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>F150</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>984</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1752340.901</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>15738.991</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Стены</t>
+          <t>Прочие_элементы</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>IfcWall</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Бетон В35</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>В35</t>
-        </is>
+          <t>Не указан</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1291</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>F150</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>611238.9129999999</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>4514.428</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1183,31 +933,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>Бетон В30 F150 W6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>984</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1752340.901</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>15738.991</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Стены</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Бетон В35 F150 W6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>611238.9129999999</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>4514.428</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Стены</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Не указан</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="D20" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>30568.661</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>2715.508</v>
       </c>
     </row>
